--- a/60 LeetCode problems to solve for coding interview.xlsx
+++ b/60 LeetCode problems to solve for coding interview.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ootsuborintarou/Documents/GitHub/LeetCode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC58061-9BF8-4946-884F-B602658C4EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E24A75-67A0-5348-B6F6-479A375DEE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="16940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="21">
   <si>
     <t>https://leetcode.com/list/xo2bgr0r</t>
   </si>
@@ -90,13 +90,19 @@
   </si>
   <si>
     <t>Others</t>
+  </si>
+  <si>
+    <t>check</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -139,6 +145,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -157,10 +176,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -169,8 +189,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -587,6 +610,9 @@
       <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="D3" s="9" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -605,6 +631,9 @@
       <c r="C5" s="7">
         <v>45534</v>
       </c>
+      <c r="D5" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="6" t="str">
@@ -614,6 +643,9 @@
       <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="D6" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="6" t="str">
@@ -623,6 +655,9 @@
       <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="D7" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="6" t="str">
@@ -632,6 +667,9 @@
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="D8" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="6" t="str">
@@ -641,9 +679,15 @@
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="D9" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="4"/>
+      <c r="A10" s="8" t="str">
+        <f>HYPERLINK("https://leetcode.com/problem-list/linked-list/", "Linked List")</f>
+        <v>Linked List</v>
+      </c>
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
@@ -658,6 +702,9 @@
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="D12" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="6" t="str">
@@ -668,7 +715,9 @@
         <v>6</v>
       </c>
       <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="D13" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -705,6 +754,9 @@
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="D16" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="6" t="str">
@@ -714,6 +766,9 @@
       <c r="B17" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="D17" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="6" t="str">
@@ -723,6 +778,9 @@
       <c r="B18" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="D18" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
@@ -736,6 +794,9 @@
       </c>
       <c r="B21" s="5" t="s">
         <v>6</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
